--- a/jogos_2024-10-31.xlsx
+++ b/jogos_2024-10-31.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Taranto</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
         <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.38</v>
+        <v>4.33</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
         <v>1.5</v>
@@ -1080,31 +1080,31 @@
         <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AC5" t="n">
         <v>2.1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['38', '43', '62', '69', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>1.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.85</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.5</v>
+        <v>2.63</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45596.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Taranto</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="M6" t="n">
         <v>3.1</v>
       </c>
       <c r="N6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.05</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
@@ -1209,31 +1209,31 @@
         <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
         <v>2.1</v>
@@ -1243,25 +1243,25 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
+          <t>['38', '43', '62', '69', '79']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG6" t="n">
-        <v>1.7</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.85</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.63</v>
+        <v>1.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45596.45833333334</v>
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Khor</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z8" t="n">
         <v>2.75</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="AA8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.33</v>
       </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD8" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['21', '76', '89']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['4', '90+6']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45596.47916666666</v>
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Khor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['4', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI9" t="n">
         <v>2</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="AJ9" t="n">
         <v>1.95</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['21', '76', '89']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45596.47916666666</v>
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="M16" t="n">
         <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
         <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.5</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.47</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AC16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI16" t="n">
         <v>2.38</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['9']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['17']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45596.60416666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z17" t="n">
         <v>1.4</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AA17" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['17']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45596.60416666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>5.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.6</v>
+        <v>5.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['72']</t>
-        </is>
-      </c>
       <c r="AG18" t="n">
-        <v>1.9</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>2.2</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.57</v>
+        <v>3.2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45596.60416666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="O19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA19" t="n">
         <v>3.75</v>
       </c>
-      <c r="P19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="AB19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.57</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['31']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45596.60416666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y24" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>5</v>
-      </c>
-      <c r="R24" t="n">
+      <c r="Z24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.4</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45596.69791666666</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>Turris Neapolis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.7</v>
       </c>
-      <c r="M25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Y25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['20']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['39', '61', '64']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45596.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M27" t="n">
         <v>2.75</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.4</v>
-      </c>
       <c r="N27" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
         <v>3.4</v>
       </c>
       <c r="P27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['28', '31', '71', '81', '90+5']</t>
+          <t>['39', '61', '64']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
         <v>2.1</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45596.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4026,80 +4026,80 @@
         <v>2.75</v>
       </c>
       <c r="M28" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O28" t="n">
         <v>3.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
         <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X28" t="n">
         <v>3.4</v>
       </c>
-      <c r="U28" t="n">
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.3</v>
       </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['28', '31', '71', '81', '90+5']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['73']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45596.69791666666</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Turris Neapolis</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
         <v>5</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.38</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T29" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W29" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X29" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['74']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45596.69791666666</v>
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,28 +4668,28 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S33" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T33" t="n">
         <v>3.75</v>
@@ -4701,16 +4701,16 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X33" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4719,14 +4719,14 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['24']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4741,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45596.88541666666</v>
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,28 +4797,28 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.53</v>
+        <v>2.25</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T34" t="n">
         <v>3.75</v>
@@ -4830,50 +4830,50 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X34" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="Y34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['24']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['46']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45596.88541666666</v>
